--- a/output/pdf_financials_xlsx/WISH.xlsx
+++ b/output/pdf_financials_xlsx/WISH.xlsx
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.087107</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.134487</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>13.125721</v>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.087107</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.134487</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-3.145322</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009346999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011382</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003084</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1181,10 +1181,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>5.496264</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1225,13 +1223,13 @@
         <v>-0.134487</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.794153</v>
+        <v>-4.784806</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.338294</v>
+        <v>-2.326912</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.799291</v>
+        <v>-1.796207</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.811661</v>
@@ -1281,13 +1279,13 @@
         <v>-0.134487</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.915177</v>
+        <v>-3.90583</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.041252</v>
+        <v>-1.02987</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.262964</v>
+        <v>-0.25988</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.8347020000000001</v>
@@ -1313,13 +1311,13 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-26.52329829232231</v>
+        <v>-26.4599772038662</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-5.084527761687994</v>
+        <v>-5.028948425481646</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1.138957156267864</v>
+        <v>-1.125599647749853</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>3.860767380141429</v>
@@ -1402,25 +1400,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.266573</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.756993</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.242453</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.692644</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.424585</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.126318</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.87888</v>
       </c>
     </row>
     <row r="35">
@@ -1458,25 +1456,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.266573</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.756993</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.17</v>
+        <v>6.412453</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.271899</v>
+        <v>2.964543</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.424585</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.126318</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.87888</v>
       </c>
     </row>
     <row r="37">
@@ -1794,25 +1792,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.288073</v>
+        <v>0.0215</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.756993</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.810695</v>
+        <v>0.568242</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.006087</v>
+        <v>0.313443</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.590977</v>
+        <v>0.166392</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.359981</v>
+        <v>0.233663</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.046975</v>
+        <v>0.168095</v>
       </c>
     </row>
     <row r="49">
@@ -4397,7 +4395,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9534,7 +9532,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -15681,7 +15679,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -17728,7 +17726,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -25000,7 +24998,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E417" s="5" t="n">
@@ -25157,7 +25155,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">

--- a/output/pdf_financials_xlsx/WISH.xlsx
+++ b/output/pdf_financials_xlsx/WISH.xlsx
@@ -11417,7 +11417,11 @@
           <t>Additions to intangible assets (Note 10)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -13240,7 +13244,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WISH.xlsx
+++ b/output/pdf_financials_xlsx/WISH.xlsx
@@ -595,10 +595,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.124095</v>
+        <v>1.338717</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.110368</v>
+        <v>1.350411</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1487,22 +1487,22 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.164289</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.289062</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.261657</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.409856</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.378517</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.290769</v>
       </c>
     </row>
     <row r="38">
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.03938</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.164289</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.169662</v>
@@ -2268,19 +2268,19 @@
         <v>0.035284</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.232444</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>2.275165</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.257657</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>2.070579</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.712675</v>
       </c>
     </row>
     <row r="65">
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.01331</v>
       </c>
     </row>
     <row r="111">
@@ -3800,10 +3800,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -3833,7 +3831,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -4126,10 +4124,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
@@ -4214,10 +4210,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.266573</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
@@ -4274,10 +4268,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.028427</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -4311,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K420"/>
+  <dimension ref="A1:K434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10682,7 +10674,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10733,7 +10729,11 @@
           <t>Deferred income tax expense (Note 11)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -12199,7 +12199,11 @@
           <t>Deferred income tax expense (Note 11)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -15208,20 +15212,26 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Cash provided by / (used in) Operating activities</t>
+        </is>
+      </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>-0.087107</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -15243,34 +15253,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J218" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K218" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Cash provided by / (used in) Operating activities</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Revenue (Note 5)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid liabilities</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -15287,127 +15299,155 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I219" s="5" t="n">
-        <v>23.088138</v>
-      </c>
-      <c r="J219" s="5" t="n">
-        <v>21.620106</v>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>14.367815</v>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Cash provided by / (used in) Operating activities</t>
+        </is>
+      </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>0.04877</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G220" s="5" t="n">
-        <v>4.780876</v>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>6.921995</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>7.898014</v>
-      </c>
-      <c r="J220" s="5" t="n">
-        <v>6.851339</v>
-      </c>
-      <c r="K220" s="5" t="n">
-        <v>4.458266</v>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Cash provided by / (used in) Operating activities</t>
+        </is>
+      </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Accrued liabilities</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>0.03141</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G221" s="5" t="n">
-        <v>9.980399</v>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>13.556839</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>15.190124</v>
-      </c>
-      <c r="J221" s="5" t="n">
-        <v>14.768767</v>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>9.909549</v>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cash provided by / (used in) Operating activities</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>General and administrative expenses (Note 6)</t>
+          <t>Cash provided by / (used in) Operating activities total</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>-0.028427</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -15424,82 +15464,96 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I222" s="5" t="n">
-        <v>11.116689</v>
-      </c>
-      <c r="J222" s="5" t="n">
-        <v>10.632104</v>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>8.738362</v>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
+          <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>0.295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G223" s="5" t="n">
-        <v>0.878976</v>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>1.297042</v>
-      </c>
-      <c r="I223" s="5" t="n">
-        <v>1.536327</v>
-      </c>
-      <c r="J223" s="5" t="n">
-        <v>1.646363</v>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>1.67856</v>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
+          <t>Cash beginning of period</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>SellingAndMarketingExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -15512,43 +15566,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G224" s="5" t="n">
-        <v>2.181702</v>
-      </c>
-      <c r="H224" s="5" t="n">
-        <v>2.986879</v>
-      </c>
-      <c r="I224" s="5" t="n">
-        <v>3.314628</v>
-      </c>
-      <c r="J224" s="5" t="n">
-        <v>2.402251</v>
-      </c>
-      <c r="K224" s="5" t="n">
-        <v>1.638783</v>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 12 &amp; 13)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash end of period $</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="n">
+        <v>0.266573</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -15565,14 +15631,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I225" s="5" t="n">
-        <v>0.598998</v>
-      </c>
-      <c r="J225" s="5" t="n">
-        <v>0.341257</v>
-      </c>
-      <c r="K225" s="5" t="n">
-        <v>-0.06346599999999999</v>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -15581,21 +15653,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>December 31, 2025 December</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -15606,20 +15670,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G226" s="5" t="n">
-        <v>13.125721</v>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>15.345557</v>
-      </c>
-      <c r="I226" s="5" t="n">
-        <v>16.566642</v>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J226" s="5" t="n">
-        <v>15.021975</v>
+        <v>0.002024</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>11.992239</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="227">
@@ -15628,19 +15698,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Operating loss</t>
+          <t>Revenue (Note 5)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -15653,20 +15719,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G227" s="5" t="n">
-        <v>-3.145322</v>
-      </c>
-      <c r="H227" s="5" t="n">
-        <v>-1.788718</v>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I227" s="5" t="n">
-        <v>-1.376518</v>
+        <v>23.088138</v>
       </c>
       <c r="J227" s="5" t="n">
-        <v>-0.253208</v>
+        <v>21.620106</v>
       </c>
       <c r="K227" s="5" t="n">
-        <v>-2.08269</v>
+        <v>14.367815</v>
       </c>
     </row>
     <row r="228">
@@ -15675,19 +15745,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -15701,21 +15767,19 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>0.009035</v>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.780876</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>6.921995</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>0.029668</v>
+        <v>7.898014</v>
       </c>
       <c r="J228" s="5" t="n">
-        <v>0.151133</v>
+        <v>6.851339</v>
       </c>
       <c r="K228" s="5" t="n">
-        <v>0.163935</v>
+        <v>4.458266</v>
       </c>
     </row>
     <row r="229">
@@ -15724,19 +15788,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Other expenses (Note 7)</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -15749,24 +15809,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G229" s="5" t="n">
+        <v>9.980399</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>13.556839</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>0.418421</v>
+        <v>15.190124</v>
       </c>
       <c r="J229" s="5" t="n">
-        <v>0.40732</v>
+        <v>14.768767</v>
       </c>
       <c r="K229" s="5" t="n">
-        <v>0.189419</v>
+        <v>9.909549</v>
       </c>
     </row>
     <row r="230">
@@ -15782,12 +15838,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>General and administrative expenses (Note 6)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -15800,20 +15856,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G230" s="5" t="n">
-        <v>-4.794153</v>
-      </c>
-      <c r="H230" s="5" t="n">
-        <v>-2.338294</v>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I230" s="5" t="n">
-        <v>-1.799291</v>
+        <v>11.116689</v>
       </c>
       <c r="J230" s="5" t="n">
-        <v>-0.811661</v>
+        <v>10.632104</v>
       </c>
       <c r="K230" s="5" t="n">
-        <v>-2.436044</v>
+        <v>8.738362</v>
       </c>
     </row>
     <row r="231">
@@ -15829,12 +15889,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Current income tax expense (Note 11)</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -15847,24 +15907,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G231" s="5" t="n">
+        <v>0.878976</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>1.297042</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>0.075629</v>
+        <v>1.536327</v>
       </c>
       <c r="J231" s="5" t="n">
-        <v>0.014369</v>
+        <v>1.646363</v>
       </c>
       <c r="K231" s="5" t="n">
-        <v>0.005133</v>
+        <v>1.67856</v>
       </c>
     </row>
     <row r="232">
@@ -15880,12 +15936,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) (Note 11)</t>
+          <t>Sales and marketing</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingAndMarketingExpense</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -15898,26 +15954,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G232" s="5" t="n">
+        <v>2.181702</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>2.986879</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>3.314628</v>
       </c>
       <c r="J232" s="5" t="n">
-        <v>0.002958</v>
+        <v>2.402251</v>
       </c>
       <c r="K232" s="5" t="n">
-        <v>-0.160492</v>
+        <v>1.638783</v>
       </c>
     </row>
     <row r="233">
@@ -15933,14 +15983,10 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (Note 12 &amp; 13)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -15951,20 +15997,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G233" s="5" t="n">
-        <v>-4.887877</v>
-      </c>
-      <c r="H233" s="5" t="n">
-        <v>-1.750129</v>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I233" s="5" t="n">
-        <v>-1.890405</v>
+        <v>0.598998</v>
       </c>
       <c r="J233" s="5" t="n">
-        <v>-0.8289879999999999</v>
+        <v>0.341257</v>
       </c>
       <c r="K233" s="5" t="n">
-        <v>-2.280685</v>
+        <v>-0.06346599999999999</v>
       </c>
     </row>
     <row r="234">
@@ -15975,15 +16025,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Other comprehensive (income) loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign operations</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -15994,24 +16048,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G234" s="5" t="n">
+        <v>13.125721</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>15.345557</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>0.001043</v>
+        <v>16.566642</v>
       </c>
       <c r="J234" s="5" t="n">
-        <v>-0.012877</v>
+        <v>15.021975</v>
       </c>
       <c r="K234" s="5" t="n">
-        <v>0.027944</v>
+        <v>11.992239</v>
       </c>
     </row>
     <row r="235">
@@ -16022,17 +16072,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Other comprehensive (income) loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -16045,24 +16095,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G235" s="5" t="n">
+        <v>-3.145322</v>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>-1.788718</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>-1.891448</v>
+        <v>-1.376518</v>
       </c>
       <c r="J235" s="5" t="n">
-        <v>-0.816111</v>
+        <v>-0.253208</v>
       </c>
       <c r="K235" s="5" t="n">
-        <v>-2.308629</v>
+        <v>-2.08269</v>
       </c>
     </row>
     <row r="236">
@@ -16073,15 +16119,19 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -16093,19 +16143,21 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>51.183732</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>52.572676</v>
+        <v>0.009035</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I236" s="5" t="n">
-        <v>53.800022</v>
+        <v>0.029668</v>
       </c>
       <c r="J236" s="5" t="n">
-        <v>54.217995</v>
+        <v>0.151133</v>
       </c>
       <c r="K236" s="5" t="n">
-        <v>54.928664</v>
+        <v>0.163935</v>
       </c>
     </row>
     <row r="237">
@@ -16116,17 +16168,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>11. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Current income tax expense</t>
+          <t>Other expenses (Note 7)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -16150,13 +16202,13 @@
         </is>
       </c>
       <c r="I237" s="5" t="n">
-        <v>0.075629</v>
+        <v>0.418421</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>0.014369</v>
+        <v>0.40732</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>0.005133</v>
+        <v>0.189419</v>
       </c>
     </row>
     <row r="238">
@@ -16167,17 +16219,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>11. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery)</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -16190,26 +16242,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G238" s="5" t="n">
+        <v>-4.794153</v>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>-2.338294</v>
+      </c>
+      <c r="I238" s="5" t="n">
+        <v>-1.799291</v>
       </c>
       <c r="J238" s="5" t="n">
-        <v>0.002958</v>
+        <v>-0.811661</v>
       </c>
       <c r="K238" s="5" t="n">
-        <v>-0.160492</v>
+        <v>-2.436044</v>
       </c>
     </row>
     <row r="239">
@@ -16220,12 +16266,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>11. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Current income tax expense (Note 11)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -16253,16 +16299,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I239" s="5" t="n">
+        <v>0.075629</v>
       </c>
       <c r="J239" s="5" t="n">
-        <v>0.017327</v>
+        <v>0.014369</v>
       </c>
       <c r="K239" s="5" t="n">
-        <v>-0.155359</v>
+        <v>0.005133</v>
       </c>
     </row>
     <row r="240">
@@ -16273,15 +16317,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>11. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Loss for the year before income tax (recovery) expense</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery) (Note 11)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -16302,14 +16350,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I240" s="5" t="n">
-        <v>-1.799291</v>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J240" s="5" t="n">
-        <v>-0.811661</v>
+        <v>0.002958</v>
       </c>
       <c r="K240" s="5" t="n">
-        <v>-2.436044</v>
+        <v>-0.160492</v>
       </c>
     </row>
     <row r="241">
@@ -16320,15 +16370,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Average statutory rate                                    27%           27%</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Recovery of income taxes based on statutory rates</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -16340,19 +16394,19 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>-1.294421</v>
+        <v>-4.887877</v>
       </c>
       <c r="H241" s="5" t="n">
-        <v>-0.631339</v>
+        <v>-1.750129</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>-0.485809</v>
+        <v>-1.890405</v>
       </c>
       <c r="J241" s="5" t="n">
-        <v>-0.219148</v>
+        <v>-0.8289879999999999</v>
       </c>
       <c r="K241" s="5" t="n">
-        <v>-0.657732</v>
+        <v>-2.280685</v>
       </c>
     </row>
     <row r="242">
@@ -16363,12 +16417,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>Other comprehensive (income) loss</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Non-taxable expenditures and other</t>
+          <t>Exchange difference on translation of foreign operations</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -16393,13 +16447,13 @@
         </is>
       </c>
       <c r="I242" s="5" t="n">
-        <v>0.165643</v>
+        <v>0.001043</v>
       </c>
       <c r="J242" s="5" t="n">
-        <v>0.026246</v>
+        <v>-0.012877</v>
       </c>
       <c r="K242" s="5" t="n">
-        <v>-0.023319</v>
+        <v>0.027944</v>
       </c>
     </row>
     <row r="243">
@@ -16410,15 +16464,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>Other comprehensive (income) loss</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>True-up for prior year losses</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -16440,13 +16498,13 @@
         </is>
       </c>
       <c r="I243" s="5" t="n">
-        <v>0.016056</v>
+        <v>-1.891448</v>
       </c>
       <c r="J243" s="5" t="n">
-        <v>-0.085495</v>
+        <v>-0.816111</v>
       </c>
       <c r="K243" s="5" t="n">
-        <v>-0.092573</v>
+        <v>-2.308629</v>
       </c>
     </row>
     <row r="244">
@@ -16457,12 +16515,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Change in non-recognized deferred tax assets</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -16476,24 +16534,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G244" s="5" t="n">
+        <v>51.183732</v>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>52.572676</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>0.41772</v>
+        <v>53.800022</v>
       </c>
       <c r="J244" s="5" t="n">
-        <v>0.341852</v>
+        <v>54.217995</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>0.6124270000000001</v>
+        <v>54.928664</v>
       </c>
     </row>
     <row r="245">
@@ -16504,15 +16558,19 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>11. Income tax</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Current income tax expense</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -16534,13 +16592,13 @@
         </is>
       </c>
       <c r="I245" s="5" t="n">
-        <v>0.009365</v>
+        <v>0.075629</v>
       </c>
       <c r="J245" s="5" t="n">
-        <v>-0.014735</v>
+        <v>0.014369</v>
       </c>
       <c r="K245" s="5" t="n">
-        <v>0.019472</v>
+        <v>0.005133</v>
       </c>
     </row>
     <row r="246">
@@ -16551,15 +16609,19 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>11. Income tax</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Rate differences</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -16580,14 +16642,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I246" s="5" t="n">
-        <v>-0.031861</v>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J246" s="5" t="n">
-        <v>-0.031393</v>
+        <v>0.002958</v>
       </c>
       <c r="K246" s="5" t="n">
-        <v>-0.013634</v>
+        <v>-0.160492</v>
       </c>
     </row>
     <row r="247">
@@ -16598,7 +16662,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>11. Income tax</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -16651,15 +16715,19 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>11. Income tax</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Losses carried forward</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Loss for the year before income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -16675,17 +16743,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="5" t="n">
-        <v>4.733573</v>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I248" s="5" t="n">
-        <v>5.42531</v>
+        <v>-1.799291</v>
       </c>
       <c r="J248" s="5" t="n">
-        <v>5.263941</v>
+        <v>-0.811661</v>
       </c>
       <c r="K248" s="5" t="n">
-        <v>5.819065</v>
+        <v>-2.436044</v>
       </c>
     </row>
     <row r="249">
@@ -16696,12 +16766,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>Average statutory rate                                    27%           27%</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Recovery of income taxes based on statutory rates</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -16715,22 +16785,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G249" s="5" t="n">
+        <v>-1.294421</v>
       </c>
       <c r="H249" s="5" t="n">
-        <v>0.672524</v>
+        <v>-0.631339</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>1.528213</v>
+        <v>-0.485809</v>
       </c>
       <c r="J249" s="5" t="n">
-        <v>2.923989</v>
+        <v>-0.219148</v>
       </c>
       <c r="K249" s="5" t="n">
-        <v>4.194617</v>
+        <v>-0.657732</v>
       </c>
     </row>
     <row r="250">
@@ -16741,12 +16809,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
+          <t>Non-taxable expenditures and other</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -16765,17 +16833,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H250" s="5" t="n">
-        <v>0.673571</v>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I250" s="5" t="n">
-        <v>0.034954</v>
+        <v>0.165643</v>
       </c>
       <c r="J250" s="5" t="n">
-        <v>0.030423</v>
+        <v>0.026246</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>0.026442</v>
+        <v>-0.023319</v>
       </c>
     </row>
     <row r="251">
@@ -16786,12 +16856,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SRED pool</t>
+          <t>True-up for prior year losses</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -16816,13 +16886,13 @@
         </is>
       </c>
       <c r="I251" s="5" t="n">
-        <v>0.311498</v>
+        <v>0.016056</v>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.63288</v>
+        <v>-0.085495</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>0.861897</v>
+        <v>-0.092573</v>
       </c>
     </row>
     <row r="252">
@@ -16833,12 +16903,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Income tax credits</t>
+          <t>Change in non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -16863,13 +16933,13 @@
         </is>
       </c>
       <c r="I252" s="5" t="n">
-        <v>0.125036</v>
+        <v>0.41772</v>
       </c>
       <c r="J252" s="5" t="n">
-        <v>0.179206</v>
+        <v>0.341852</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>0.344285</v>
+        <v>0.6124270000000001</v>
       </c>
     </row>
     <row r="253">
@@ -16880,7 +16950,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -16904,17 +16974,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H253" s="5" t="n">
-        <v>0.053383</v>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I253" s="5" t="n">
-        <v>0.176597</v>
+        <v>0.009365</v>
       </c>
       <c r="J253" s="5" t="n">
-        <v>0.133758</v>
+        <v>-0.014735</v>
       </c>
       <c r="K253" s="5" t="n">
-        <v>0.053145</v>
+        <v>0.019472</v>
       </c>
     </row>
     <row r="254">
@@ -16925,12 +16997,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Total unrecognized temporary deductible differences</t>
+          <t>Rate differences</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -16949,17 +17021,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H254" s="5" t="n">
-        <v>6.133051</v>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I254" s="5" t="n">
-        <v>8.227802000000001</v>
+        <v>-0.031861</v>
       </c>
       <c r="J254" s="5" t="n">
-        <v>9.164197</v>
+        <v>-0.031393</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>11.299451</v>
+        <v>-0.013634</v>
       </c>
     </row>
     <row r="255">
@@ -16970,15 +17044,19 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -16989,20 +17067,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G255" s="5" t="n">
-        <v>0.218107</v>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>-0.000161</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>-0.000143</v>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J255" s="5" t="n">
-        <v>-8.4e-05</v>
+        <v>0.017327</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>-1.6e-05</v>
+        <v>-0.155359</v>
       </c>
     </row>
     <row r="256">
@@ -17013,12 +17097,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Losses carried forward</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -17032,20 +17116,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G256" s="5" t="n">
-        <v>-1.354101</v>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H256" s="5" t="n">
-        <v>-0.394316</v>
+        <v>4.733573</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>-0.202104</v>
+        <v>5.42531</v>
       </c>
       <c r="J256" s="5" t="n">
-        <v>-0.150261</v>
+        <v>5.263941</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>-0.101676</v>
+        <v>5.819065</v>
       </c>
     </row>
     <row r="257">
@@ -17056,12 +17142,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Non-capital losses/non-operating losses</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -17075,20 +17161,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G257" s="5" t="n">
-        <v>0.597108</v>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>0.520967</v>
+        <v>0.672524</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>0.314589</v>
+        <v>1.528213</v>
       </c>
       <c r="J257" s="5" t="n">
-        <v>0.249444</v>
+        <v>2.923989</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>0.371773</v>
+        <v>4.194617</v>
       </c>
     </row>
     <row r="258">
@@ -17099,12 +17187,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Property and equipment</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -17124,16 +17212,16 @@
         </is>
       </c>
       <c r="H258" s="5" t="n">
-        <v>0.02044</v>
+        <v>0.673571</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>0.019103</v>
+        <v>0.034954</v>
       </c>
       <c r="J258" s="5" t="n">
-        <v>0.029388</v>
+        <v>0.030423</v>
       </c>
       <c r="K258" s="5" t="n">
-        <v>0.02684</v>
+        <v>0.026442</v>
       </c>
     </row>
     <row r="259">
@@ -17144,12 +17232,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Convertible debt (equity component)</t>
+          <t>SRED pool</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -17173,18 +17261,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I259" s="5" t="n">
+        <v>0.311498</v>
+      </c>
+      <c r="J259" s="5" t="n">
+        <v>0.63288</v>
       </c>
       <c r="K259" s="5" t="n">
-        <v>-0.175612</v>
+        <v>0.861897</v>
       </c>
     </row>
     <row r="260">
@@ -17195,12 +17279,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Income tax credits</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -17214,20 +17298,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G260" s="5" t="n">
-        <v>-0.384205</v>
-      </c>
-      <c r="H260" s="5" t="n">
-        <v>0.14693</v>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I260" s="5" t="n">
-        <v>0.131445</v>
+        <v>0.125036</v>
       </c>
       <c r="J260" s="5" t="n">
-        <v>0.128487</v>
+        <v>0.179206</v>
       </c>
       <c r="K260" s="5" t="n">
-        <v>0.121309</v>
+        <v>0.344285</v>
       </c>
     </row>
     <row r="261">
@@ -17238,12 +17326,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>of $0.05 for total cash proceeds of $2,595.</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Company may, during the 12-month period commencing July 15, 2024, and ending July</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -17262,21 +17350,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H261" s="5" t="n">
+        <v>0.053383</v>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>0.176597</v>
       </c>
       <c r="J261" s="5" t="n">
-        <v>0.002025</v>
+        <v>0.133758</v>
       </c>
       <c r="K261" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>0.053145</v>
       </c>
     </row>
     <row r="262">
@@ -17287,12 +17371,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>of $0.05 for total cash proceeds of $2,595.</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>purchase up to 2,707,931 Shares in total, being 5% of the total number of 54,158,620 Shares outstanding as at June</t>
+          <t>Total unrecognized temporary deductible differences</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -17311,21 +17395,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H262" s="5" t="n">
+        <v>6.133051</v>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>8.227802000000001</v>
       </c>
       <c r="J262" s="5" t="n">
-        <v>0.002024</v>
+        <v>9.164197</v>
       </c>
       <c r="K262" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>11.299451</v>
       </c>
     </row>
     <row r="263">
@@ -17336,12 +17416,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>exercise price</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>January 1, 2024</t>
+          <t>Property and equipment</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -17355,26 +17435,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G263" s="5" t="n">
+        <v>0.218107</v>
+      </c>
+      <c r="H263" s="5" t="n">
+        <v>-0.000161</v>
+      </c>
+      <c r="I263" s="5" t="n">
+        <v>-0.000143</v>
       </c>
       <c r="J263" s="5" t="n">
-        <v>1.83e-06</v>
+        <v>-8.4e-05</v>
       </c>
       <c r="K263" s="5" t="n">
-        <v>2.80305</v>
+        <v>-1.6e-05</v>
       </c>
     </row>
     <row r="264">
@@ -17385,12 +17459,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>exercise price</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Forfeited/expired</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -17404,26 +17478,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G264" s="5" t="n">
+        <v>-1.354101</v>
+      </c>
+      <c r="H264" s="5" t="n">
+        <v>-0.394316</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>-0.202104</v>
       </c>
       <c r="J264" s="5" t="n">
-        <v>1.48e-06</v>
+        <v>-0.150261</v>
       </c>
       <c r="K264" s="5" t="n">
-        <v>-0.31</v>
+        <v>-0.101676</v>
       </c>
     </row>
     <row r="265">
@@ -17434,12 +17502,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>exercise price</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>December 31, 2024</t>
+          <t>Non-capital losses/non-operating losses</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -17453,26 +17521,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G265" s="5" t="n">
+        <v>0.597108</v>
+      </c>
+      <c r="H265" s="5" t="n">
+        <v>0.520967</v>
+      </c>
+      <c r="I265" s="5" t="n">
+        <v>0.314589</v>
       </c>
       <c r="J265" s="5" t="n">
-        <v>1.87e-06</v>
+        <v>0.249444</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>2.49305</v>
+        <v>0.371773</v>
       </c>
     </row>
     <row r="266">
@@ -17483,12 +17545,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>exercise price</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Granted</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -17507,21 +17569,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H266" s="5" t="n">
+        <v>0.02044</v>
+      </c>
+      <c r="I266" s="5" t="n">
+        <v>0.019103</v>
       </c>
       <c r="J266" s="5" t="n">
-        <v>1.7e-07</v>
+        <v>0.029388</v>
       </c>
       <c r="K266" s="5" t="n">
-        <v>0.05</v>
+        <v>0.02684</v>
       </c>
     </row>
     <row r="267">
@@ -17532,12 +17590,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>exercise price</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Exercised</t>
+          <t>Convertible debt (equity component)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -17566,11 +17624,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J267" s="5" t="n">
-        <v>5e-08</v>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>-0.051904</v>
+        <v>-0.175612</v>
       </c>
     </row>
     <row r="268">
@@ -17581,12 +17641,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>exercise price</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>December 31, 2025</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -17600,26 +17660,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G268" s="5" t="n">
+        <v>-0.384205</v>
+      </c>
+      <c r="H268" s="5" t="n">
+        <v>0.14693</v>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>0.131445</v>
       </c>
       <c r="J268" s="5" t="n">
-        <v>1.87e-06</v>
+        <v>0.128487</v>
       </c>
       <c r="K268" s="5" t="n">
-        <v>2.245581</v>
+        <v>0.121309</v>
       </c>
     </row>
     <row r="269">
@@ -17630,12 +17684,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>of $0.05 for total cash proceeds of $2,595.</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>May 26, 2025 50,000 $0.17 4.0 May</t>
+          <t>Company may, during the 12-month period commencing July 15, 2024, and ending July</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -17665,10 +17719,10 @@
         </is>
       </c>
       <c r="J269" s="5" t="n">
-        <v>0.00203</v>
+        <v>0.002025</v>
       </c>
       <c r="K269" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="270">
@@ -17677,10 +17731,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>of $0.05 for total cash proceeds of $2,595.</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>December 31, 2024 December</t>
+          <t>purchase up to 2,707,931 Shares in total, being 5% of the total number of 54,158,620 Shares outstanding as at June</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -17704,16 +17762,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I270" s="5" t="n">
-        <v>0.002023</v>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J270" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>2.6e-05</v>
       </c>
     </row>
     <row r="271">
@@ -17724,19 +17782,15 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>exercise price</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>January 1, 2024</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -17747,24 +17801,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G271" s="5" t="n">
-        <v>-0.009346999999999999</v>
-      </c>
-      <c r="H271" s="5" t="n">
-        <v>-0.011382</v>
-      </c>
-      <c r="I271" s="5" t="n">
-        <v>-0.003084</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>1.83e-06</v>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>2.80305</v>
       </c>
     </row>
     <row r="272">
@@ -17775,12 +17831,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>exercise price</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Remeasurement of contingent consideration liability</t>
+          <t>Forfeited/expired</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -17794,24 +17850,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G272" s="5" t="n">
-        <v>0.859672</v>
-      </c>
-      <c r="H272" s="5" t="n">
-        <v>-0.09571499999999999</v>
-      </c>
-      <c r="I272" s="5" t="n">
-        <v>-0.022232</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" s="5" t="n">
+        <v>1.48e-06</v>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="273">
@@ -17822,19 +17880,15 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>exercise price</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (Note 11)</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>December 31, 2024</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -17855,16 +17909,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I273" s="5" t="n">
-        <v>0.015485</v>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J273" s="5" t="n">
-        <v>0.002958</v>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.87e-06</v>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>2.49305</v>
       </c>
     </row>
     <row r="274">
@@ -17875,19 +17929,15 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>11. Income tax</t>
+          <t>exercise price</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Deferred income tax expense</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Granted</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -17908,16 +17958,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I274" s="5" t="n">
-        <v>0.015485</v>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J274" s="5" t="n">
-        <v>0.002958</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.7e-07</v>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="275">
@@ -17928,19 +17978,15 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>11. Income tax</t>
+          <t>exercise price</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Exercised</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -17961,16 +18007,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I275" s="5" t="n">
-        <v>0.091114</v>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J275" s="5" t="n">
-        <v>0.017327</v>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-08</v>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>-0.051904</v>
       </c>
     </row>
     <row r="276">
@@ -17981,19 +18027,15 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Increase (decrease) in income tax recovery from</t>
+          <t>exercise price</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>December 31, 2025</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -18014,16 +18056,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I276" s="5" t="n">
-        <v>0.091114</v>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J276" s="5" t="n">
-        <v>0.017327</v>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.87e-06</v>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>2.245581</v>
       </c>
     </row>
     <row r="277">
@@ -18034,12 +18076,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Non-recognized deferred tax assets</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Contingent liability</t>
+          <t>May 26, 2025 50,000 $0.17 4.0 May</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -18063,18 +18105,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I277" s="5" t="n">
-        <v>0.099353</v>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" s="5" t="n">
+        <v>0.00203</v>
+      </c>
+      <c r="K277" s="5" t="n">
+        <v>2.6e-05</v>
       </c>
     </row>
     <row r="278">
@@ -18083,14 +18123,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Non-recognized deferred tax assets</t>
-        </is>
-      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Financing costs</t>
+          <t>December 31, 2024 December</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -18115,12 +18151,10 @@
         </is>
       </c>
       <c r="I278" s="5" t="n">
-        <v>0.526841</v>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="J278" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -18136,15 +18170,19 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>53,983,620) common shares.</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Company may, during the 12-month period commencing July 15, 2024, and ending July</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -18155,21 +18193,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G279" s="5" t="n">
+        <v>-0.009346999999999999</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>-0.011382</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="J279" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>-0.003084</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -18185,12 +18221,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>53,983,620) common shares.</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>purchase up to 2,707,931 Shares in total, being 5% of the total number of 54,158,620 Shares outstanding as at June</t>
+          <t>Remeasurement of contingent consideration liability</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -18204,21 +18240,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G280" s="5" t="n">
+        <v>0.859672</v>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>-0.09571499999999999</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="J280" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>-0.022232</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -18234,15 +18268,19 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>of the Company.</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>month period commencing June 30, 2023 and ending June 29, 2024, purchase up to 2,688,431 Shares in total, being 5% of the total number of 53,768,620 Shares outstanding as at June</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Deferred income tax expense (Note 11)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -18264,10 +18302,10 @@
         </is>
       </c>
       <c r="I281" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.015485</v>
       </c>
       <c r="J281" s="5" t="n">
-        <v>1.2e-05</v>
+        <v>0.002958</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -18283,15 +18321,19 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>d) Warrants</t>
+          <t>11. Income tax</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>The changes in warrants during the year ended December 31, 2024 and the year ended December</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Deferred income tax expense</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -18313,10 +18355,10 @@
         </is>
       </c>
       <c r="I282" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.015485</v>
       </c>
       <c r="J282" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.002958</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -18332,15 +18374,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>were as follows</t>
+          <t>11. Income tax</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>December 31, 2024 December</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -18362,10 +18408,10 @@
         </is>
       </c>
       <c r="I283" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.091114</v>
       </c>
       <c r="J283" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.017327</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -18381,15 +18427,19 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Balance outstanding,</t>
+          <t>Increase (decrease) in income tax recovery from</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Balance outstanding, beginning of year - -</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -18411,10 +18461,10 @@
         </is>
       </c>
       <c r="I284" s="5" t="n">
-        <v>1.75e-06</v>
+        <v>0.091114</v>
       </c>
       <c r="J284" s="5" t="n">
-        <v>0.313766</v>
+        <v>0.017327</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -18430,12 +18480,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Balance outstanding,</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Broker Warrants exercised - -</t>
+          <t>Contingent liability</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -18454,14 +18504,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H285" s="5" t="n">
-        <v>7.5e-07</v>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I285" s="5" t="n">
-        <v>1.75e-06</v>
-      </c>
-      <c r="J285" s="5" t="n">
-        <v>-0.313766</v>
+        <v>0.099353</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -18477,12 +18531,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Balance outstanding, end</t>
+          <t>Non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Balance outstanding, end of year - -</t>
+          <t>Financing costs</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -18501,11 +18555,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H286" s="5" t="n">
-        <v>1.75e-06</v>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I286" s="5" t="n">
-        <v>0.313766</v>
+        <v>0.526841</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -18524,10 +18580,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>53,983,620) common shares.</t>
+        </is>
+      </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>December 31, 2023 December</t>
+          <t>Company may, during the 12-month period commencing July 15, 2024, and ending July</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -18546,16 +18606,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H287" s="5" t="n">
-        <v>0.002022</v>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I287" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002025</v>
+      </c>
+      <c r="J287" s="5" t="n">
+        <v>1.4e-05</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -18569,17 +18629,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>53,983,620) common shares.</t>
+        </is>
+      </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Revenue (Note 7)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>purchase up to 2,707,931 Shares in total, being 5% of the total number of 54,158,620 Shares outstanding as at June</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -18595,16 +18655,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H288" s="5" t="n">
-        <v>20.478834</v>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I288" s="5" t="n">
-        <v>23.088138</v>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="J288" s="5" t="n">
+        <v>2.6e-05</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -18620,19 +18680,15 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>of the Company.</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>General and administrative expenses (Note 8)</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>month period commencing June 30, 2023 and ending June 29, 2024, purchase up to 2,688,431 Shares in total, being 5% of the total number of 53,768,620 Shares outstanding as at June</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -18648,16 +18704,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H289" s="5" t="n">
-        <v>9.922293</v>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I289" s="5" t="n">
-        <v>11.116689</v>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="J289" s="5" t="n">
+        <v>1.2e-05</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -18673,12 +18729,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>d) Warrants</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 14 &amp; 15)</t>
+          <t>The changes in warrants during the year ended December 31, 2024 and the year ended December</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -18697,16 +18753,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" s="5" t="n">
-        <v>1.139343</v>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I290" s="5" t="n">
-        <v>0.598998</v>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="J290" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -18722,19 +18778,15 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>were as follows</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Other expenses (Note 9)</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>December 31, 2024 December</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -18750,16 +18802,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H291" s="5" t="n">
-        <v>0.656673</v>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I291" s="5" t="n">
-        <v>0.418421</v>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="J291" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -18775,19 +18827,15 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Balance outstanding,</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Current income tax expense (recovery) (Note 13)</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Balance outstanding, beginning of year - -</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -18803,16 +18851,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H292" s="5" t="n">
-        <v>-0.057031</v>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I292" s="5" t="n">
-        <v>0.075629</v>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.75e-06</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>0.313766</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -18828,19 +18876,15 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Balance outstanding,</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) (Note 13)</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Broker Warrants exercised - -</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -18857,15 +18901,13 @@
         </is>
       </c>
       <c r="H293" s="5" t="n">
-        <v>-0.531134</v>
+        <v>7.5e-07</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>0.015485</v>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.75e-06</v>
+      </c>
+      <c r="J293" s="5" t="n">
+        <v>-0.313766</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -18881,12 +18923,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Other comprehensive loss (income)</t>
+          <t>Balance outstanding, end</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign operations</t>
+          <t>Balance outstanding, end of year - -</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -18906,10 +18948,10 @@
         </is>
       </c>
       <c r="H294" s="5" t="n">
-        <v>-0.036358</v>
+        <v>1.75e-06</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>0.001043</v>
+        <v>0.313766</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -18928,21 +18970,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Other comprehensive loss (income)</t>
-        </is>
-      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>December 31, 2023 December</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -18959,10 +18993,10 @@
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>-1.713771</v>
+        <v>0.002022</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>-1.891448</v>
+        <v>3.1e-05</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -18981,19 +19015,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>13. Income tax</t>
-        </is>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Current income tax expense (recovery)</t>
+          <t>Revenue (Note 7)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -19012,10 +19042,10 @@
         </is>
       </c>
       <c r="H296" s="5" t="n">
-        <v>-0.057031</v>
+        <v>20.478834</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>0.075629</v>
+        <v>23.088138</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -19036,17 +19066,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery)</t>
+          <t>General and administrative expenses (Note 8)</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -19065,10 +19095,10 @@
         </is>
       </c>
       <c r="H297" s="5" t="n">
-        <v>-0.531134</v>
+        <v>9.922293</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>0.015485</v>
+        <v>11.116689</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -19089,19 +19119,15 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (Note 14 &amp; 15)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -19118,10 +19144,10 @@
         </is>
       </c>
       <c r="H298" s="5" t="n">
-        <v>-0.588165</v>
+        <v>1.139343</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>0.091114</v>
+        <v>0.598998</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -19142,15 +19168,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>13. Income tax</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Loss for the year before income tax (recovery) expense</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>Other expenses (Note 9)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -19167,10 +19197,10 @@
         </is>
       </c>
       <c r="H299" s="5" t="n">
-        <v>-2.338294</v>
+        <v>0.656673</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>-1.799291</v>
+        <v>0.418421</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -19191,15 +19221,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Non-taxable expenditures and other</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Current income tax expense (recovery) (Note 13)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -19210,14 +19244,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G300" s="5" t="n">
-        <v>0.758109</v>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H300" s="5" t="n">
-        <v>0.245774</v>
+        <v>-0.057031</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>0.165643</v>
+        <v>0.075629</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -19238,15 +19274,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>True-up for prior year losses</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery) (Note 13)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -19263,10 +19303,10 @@
         </is>
       </c>
       <c r="H301" s="5" t="n">
-        <v>-0.691813</v>
+        <v>-0.531134</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>0.016056</v>
+        <v>0.015485</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -19287,12 +19327,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>Other comprehensive loss (income)</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Change in non-recognized deferred tax assets</t>
+          <t>Exchange difference on translation of foreign operations</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -19306,14 +19346,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G302" s="5" t="n">
-        <v>0.630036</v>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H302" s="5" t="n">
-        <v>0.547455</v>
+        <v>-0.036358</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>0.41772</v>
+        <v>0.001043</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -19334,15 +19376,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>Other comprehensive loss (income)</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -19359,10 +19405,10 @@
         </is>
       </c>
       <c r="H303" s="5" t="n">
-        <v>-0.04404</v>
+        <v>-1.713771</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>0.009365</v>
+        <v>-1.891448</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -19383,15 +19429,19 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>13. Income tax</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Rate differences</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Current income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -19408,10 +19458,10 @@
         </is>
       </c>
       <c r="H304" s="5" t="n">
-        <v>-0.014202</v>
+        <v>-0.057031</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>-0.031861</v>
+        <v>0.075629</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -19432,12 +19482,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>13. Income tax</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -19461,10 +19511,10 @@
         </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>-0.588165</v>
+        <v>-0.531134</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>0.091114</v>
+        <v>0.015485</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -19485,15 +19535,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>53,705,324) common shares.</t>
+          <t>13. Income tax</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>month period commencing June 30, 2023 and ending June 29, 2024, purchase up to 2,688,431 Shares in total, being 5% of the total number of 53,768,620 Shares outstanding as at June</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -19510,10 +19564,10 @@
         </is>
       </c>
       <c r="H306" s="5" t="n">
-        <v>0.002023</v>
+        <v>-0.588165</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>1.2e-05</v>
+        <v>0.091114</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -19534,15 +19588,19 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>respectively.</t>
+          <t>13. Income tax</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>make a Normal Course Issuer Bid (“NCIB”) was approved by the Exchange. Under the renewed NCIB, the Company may, during the 12-month period commencing June 20, 2022 and ending June</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
+          <t>Loss for the year before income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -19553,14 +19611,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G307" s="5" t="n">
-        <v>0.002023</v>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>0.002023</v>
+        <v>-2.338294</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>-1.799291</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -19581,12 +19641,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>d) Warrants</t>
+          <t>Increase in income tax recovery resulting from</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>The changes in warrants during the year ended December 31, 2023 and the year ended December</t>
+          <t>Non-taxable expenditures and other</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -19600,16 +19660,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G308" s="5" t="n">
+        <v>0.758109</v>
       </c>
       <c r="H308" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.245774</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.165643</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -19630,12 +19688,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>were as follows</t>
+          <t>Increase in income tax recovery resulting from</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>December 31, 2023 December</t>
+          <t>True-up for prior year losses</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -19655,10 +19713,10 @@
         </is>
       </c>
       <c r="H309" s="5" t="n">
-        <v>0.002022</v>
+        <v>-0.691813</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.016056</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -19679,12 +19737,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Balance outstanding,</t>
+          <t>Increase in income tax recovery resulting from</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Balance outstanding, beginning of year 313,766 1.75</t>
+          <t>Change in non-recognized deferred tax assets</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -19698,16 +19756,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G310" s="5" t="n">
+        <v>0.630036</v>
       </c>
       <c r="H310" s="5" t="n">
-        <v>1.43e-06</v>
+        <v>0.547455</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>0.460365</v>
+        <v>0.41772</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -19728,12 +19784,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Balance outstanding,</t>
+          <t>Increase in income tax recovery resulting from</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Broker Warrants expired (313,766) 1.75</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -19753,10 +19809,10 @@
         </is>
       </c>
       <c r="H311" s="5" t="n">
-        <v>7.5e-07</v>
+        <v>-0.04404</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>-0.076489</v>
+        <v>0.009365</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -19775,10 +19831,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Increase in income tax recovery resulting from</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>December 31, 2022 December</t>
+          <t>Rate differences</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -19792,16 +19852,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G312" s="5" t="n">
-        <v>0.002021</v>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H312" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.014202</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>-0.031861</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -19820,15 +19880,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Increase in income tax recovery resulting from</t>
+        </is>
+      </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Revenue (Note 6)</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -19841,16 +19905,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G313" s="5" t="n">
-        <v>14.761275</v>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H313" s="5" t="n">
-        <v>20.478834</v>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.588165</v>
+      </c>
+      <c r="I313" s="5" t="n">
+        <v>0.091114</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -19871,19 +19935,15 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>53,705,324) common shares.</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>General and administrative expenses (Note 7)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>month period commencing June 30, 2023 and ending June 29, 2024, purchase up to 2,688,431 Shares in total, being 5% of the total number of 53,768,620 Shares outstanding as at June</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -19894,16 +19954,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G314" s="5" t="n">
-        <v>7.742308</v>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H314" s="5" t="n">
-        <v>9.922293</v>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>1.2e-05</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -19924,12 +19984,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>respectively.</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 13 &amp; 14)</t>
+          <t>make a Normal Course Issuer Bid (“NCIB”) was approved by the Exchange. Under the renewed NCIB, the Company may, during the 12-month period commencing June 20, 2022 and ending June</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -19944,15 +20004,13 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>2.322735</v>
+        <v>0.002023</v>
       </c>
       <c r="H315" s="5" t="n">
-        <v>1.139343</v>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="I315" s="5" t="n">
+        <v>1.9e-05</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -19973,19 +20031,15 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>d) Warrants</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Other expenses (Note 8)</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>The changes in warrants during the year ended December 31, 2023 and the year ended December</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -19996,16 +20050,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G316" s="5" t="n">
-        <v>0.789471</v>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H316" s="5" t="n">
-        <v>0.656673</v>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="I316" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -20026,12 +20080,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>were as follows</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Current income tax (recovery) expense</t>
+          <t>December 31, 2023 December</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -20045,16 +20099,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G317" s="5" t="n">
-        <v>0.133746</v>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H317" s="5" t="n">
-        <v>-0.057031</v>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="I317" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -20075,12 +20129,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Balance outstanding,</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Balance outstanding, beginning of year 313,766 1.75</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -20094,16 +20148,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G318" s="5" t="n">
-        <v>-0.040022</v>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H318" s="5" t="n">
-        <v>-0.531134</v>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.43e-06</v>
+      </c>
+      <c r="I318" s="5" t="n">
+        <v>0.460365</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -20124,12 +20178,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Balance outstanding,</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign operations</t>
+          <t>Broker Warrants expired (313,766) 1.75</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -20149,12 +20203,10 @@
         </is>
       </c>
       <c r="H319" s="5" t="n">
-        <v>-0.036358</v>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.5e-07</v>
+      </c>
+      <c r="I319" s="5" t="n">
+        <v>-0.076489</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -20173,21 +20225,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>December 31, 2022 December</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -20199,10 +20243,10 @@
         </is>
       </c>
       <c r="G320" s="5" t="n">
-        <v>-4.887877</v>
+        <v>0.002021</v>
       </c>
       <c r="H320" s="5" t="n">
-        <v>-1.713771</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -20226,17 +20270,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>comprehensive loss.</t>
-        </is>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>to fair value at each reporting date, until such time as the earn-out period is over, with changes to fair value statements of loss and comprehensive loss for the years ended December 31, 2022 and December</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
+          <t>Revenue (Note 6)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -20248,10 +20292,10 @@
         </is>
       </c>
       <c r="G321" s="5" t="n">
-        <v>0.002021</v>
+        <v>14.761275</v>
       </c>
       <c r="H321" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>20.478834</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -20277,15 +20321,19 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>6. Geographic information</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>December 31, 2022 December</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>General and administrative expenses (Note 7)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -20297,10 +20345,10 @@
         </is>
       </c>
       <c r="G322" s="5" t="n">
-        <v>0.002021</v>
+        <v>7.742308</v>
       </c>
       <c r="H322" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>9.922293</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -20326,12 +20374,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>6. Geographic information</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Stock-based compensation (Note 13 &amp; 14)</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -20346,10 +20394,10 @@
         </is>
       </c>
       <c r="G323" s="5" t="n">
-        <v>11.54163</v>
+        <v>2.322735</v>
       </c>
       <c r="H323" s="5" t="n">
-        <v>14.471193</v>
+        <v>1.139343</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -20375,15 +20423,19 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>6. Geographic information</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Other expenses (Note 8)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -20395,10 +20447,10 @@
         </is>
       </c>
       <c r="G324" s="5" t="n">
-        <v>1.423865</v>
+        <v>0.789471</v>
       </c>
       <c r="H324" s="5" t="n">
-        <v>2.769625</v>
+        <v>0.656673</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -20424,15 +20476,19 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>6. Geographic information</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Current income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -20444,10 +20500,10 @@
         </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>1.79578</v>
+        <v>0.133746</v>
       </c>
       <c r="H325" s="5" t="n">
-        <v>3.238016</v>
+        <v>-0.057031</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -20473,15 +20529,19 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>6. Geographic information</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -20493,10 +20553,10 @@
         </is>
       </c>
       <c r="G326" s="5" t="n">
-        <v>14.761275</v>
+        <v>-0.040022</v>
       </c>
       <c r="H326" s="5" t="n">
-        <v>20.478834</v>
+        <v>-0.531134</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -20522,12 +20582,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>6. Geographic information</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>December 31, 2022 or December</t>
+          <t>Exchange difference on translation of foreign operations</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -20541,11 +20601,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G327" s="5" t="n">
-        <v>0.002021</v>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H327" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.036358</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -20571,15 +20633,19 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7. General and administrative expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>The following shows the details of general and administrative expenses for the years ended December</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -20591,10 +20657,10 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>0.002022</v>
+        <v>-4.887877</v>
       </c>
       <c r="H328" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-1.713771</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -20620,12 +20686,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>comprehensive loss.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>December 31, 2022 December</t>
+          <t>to fair value at each reporting date, until such time as the earn-out period is over, with changes to fair value statements of loss and comprehensive loss for the years ended December 31, 2022 and December</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -20669,19 +20735,15 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>6. Geographic information</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>December 31, 2022 December</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -20693,10 +20755,10 @@
         </is>
       </c>
       <c r="G330" s="5" t="n">
-        <v>1.030486</v>
+        <v>0.002021</v>
       </c>
       <c r="H330" s="5" t="n">
-        <v>1.020312</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -20722,19 +20784,15 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>6. Geographic information</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -20746,10 +20804,10 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>0.670285</v>
+        <v>11.54163</v>
       </c>
       <c r="H331" s="5" t="n">
-        <v>0.688422</v>
+        <v>14.471193</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -20775,12 +20833,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>6. Geographic information</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Property tax</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -20795,12 +20853,10 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>0.07795100000000001</v>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.423865</v>
+      </c>
+      <c r="H332" s="5" t="n">
+        <v>2.769625</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -20826,12 +20882,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>6. Geographic information</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Salaries, wages, employee benefits</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -20846,10 +20902,10 @@
         </is>
       </c>
       <c r="G333" s="5" t="n">
-        <v>3.039188</v>
+        <v>1.79578</v>
       </c>
       <c r="H333" s="5" t="n">
-        <v>4.239243</v>
+        <v>3.238016</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -20875,12 +20931,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>6. Geographic information</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Software subscriptions</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -20895,10 +20951,10 @@
         </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>0.914162</v>
+        <v>14.761275</v>
       </c>
       <c r="H334" s="5" t="n">
-        <v>1.583838</v>
+        <v>20.478834</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -20924,12 +20980,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>6. Geographic information</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Subcontractor expenses</t>
+          <t>December 31, 2022 or December</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -20944,10 +21000,10 @@
         </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2.010236</v>
+        <v>0.002021</v>
       </c>
       <c r="H335" s="5" t="n">
-        <v>2.390478</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -20973,12 +21029,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>and 2021</t>
+          <t>7. General and administrative expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>The following shows the details of general and administrative expenses for the years ended December</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -20993,10 +21049,10 @@
         </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>7.742308</v>
+        <v>0.002022</v>
       </c>
       <c r="H336" s="5" t="n">
-        <v>9.922293</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -21022,7 +21078,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21071,15 +21127,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Acquisition related expenses</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -21091,10 +21151,10 @@
         </is>
       </c>
       <c r="G338" s="5" t="n">
-        <v>0.177537</v>
+        <v>1.030486</v>
       </c>
       <c r="H338" s="5" t="n">
-        <v>0.144</v>
+        <v>1.020312</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -21120,15 +21180,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Financing set-up fees</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -21140,10 +21204,10 @@
         </is>
       </c>
       <c r="G339" s="5" t="n">
-        <v>0.16016</v>
+        <v>0.670285</v>
       </c>
       <c r="H339" s="5" t="n">
-        <v>0.029565</v>
+        <v>0.688422</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -21169,19 +21233,15 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Property tax</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -21193,10 +21253,12 @@
         </is>
       </c>
       <c r="G340" s="5" t="n">
-        <v>0.093609</v>
-      </c>
-      <c r="H340" s="5" t="n">
-        <v>0.090056</v>
+        <v>0.07795100000000001</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -21222,12 +21284,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Foreign currency losses</t>
+          <t>Salaries, wages, employee benefits</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -21242,10 +21304,10 @@
         </is>
       </c>
       <c r="G341" s="5" t="n">
-        <v>0.036116</v>
+        <v>3.039188</v>
       </c>
       <c r="H341" s="5" t="n">
-        <v>0.305056</v>
+        <v>4.239243</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -21271,19 +21333,15 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Software subscriptions</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -21295,10 +21353,10 @@
         </is>
       </c>
       <c r="G342" s="5" t="n">
-        <v>0.322049</v>
+        <v>0.914162</v>
       </c>
       <c r="H342" s="5" t="n">
-        <v>0.087996</v>
+        <v>1.583838</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -21324,12 +21382,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>8. Other expenses</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Subcontractor expenses</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -21344,10 +21402,10 @@
         </is>
       </c>
       <c r="G343" s="5" t="n">
-        <v>0.789471</v>
+        <v>2.010236</v>
       </c>
       <c r="H343" s="5" t="n">
-        <v>0.656673</v>
+        <v>2.390478</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -21373,12 +21431,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>9. Accounts and other receivables</t>
+          <t>and 2021</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>December 31, 2022 December</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -21393,10 +21451,10 @@
         </is>
       </c>
       <c r="G344" s="5" t="n">
-        <v>0.002021</v>
+        <v>7.742308</v>
       </c>
       <c r="H344" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>9.922293</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -21422,12 +21480,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>9. Accounts and other receivables</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>December 31, 2022 December</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -21442,10 +21500,10 @@
         </is>
       </c>
       <c r="G345" s="5" t="n">
-        <v>0.289062</v>
+        <v>0.002021</v>
       </c>
       <c r="H345" s="5" t="n">
-        <v>0.261657</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -21471,12 +21529,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>9. Accounts and other receivables</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Provision for expected credit losses</t>
+          <t>Acquisition related expenses</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -21491,10 +21549,10 @@
         </is>
       </c>
       <c r="G346" s="5" t="n">
-        <v>-0.1194</v>
+        <v>0.177537</v>
       </c>
       <c r="H346" s="5" t="n">
-        <v>-0.083325</v>
+        <v>0.144</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -21520,12 +21578,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>9. Accounts and other receivables</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Accounts and other receivables</t>
+          <t>Financing set-up fees</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -21540,10 +21598,10 @@
         </is>
       </c>
       <c r="G347" s="5" t="n">
-        <v>0.169662</v>
+        <v>0.16016</v>
       </c>
       <c r="H347" s="5" t="n">
-        <v>0.178332</v>
+        <v>0.029565</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -21569,15 +21627,19 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>12. Income tax</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Current income tax (recovery) expense</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -21589,10 +21651,10 @@
         </is>
       </c>
       <c r="G348" s="5" t="n">
-        <v>0.133746</v>
+        <v>0.093609</v>
       </c>
       <c r="H348" s="5" t="n">
-        <v>-0.057031</v>
+        <v>0.090056</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -21618,12 +21680,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>12. Income tax</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Foreign currency losses</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -21638,10 +21700,10 @@
         </is>
       </c>
       <c r="G349" s="5" t="n">
-        <v>-0.040022</v>
+        <v>0.036116</v>
       </c>
       <c r="H349" s="5" t="n">
-        <v>-0.531134</v>
+        <v>0.305056</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -21667,15 +21729,19 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>12. Income tax</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Income tax (recovery) expense</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -21687,10 +21753,10 @@
         </is>
       </c>
       <c r="G350" s="5" t="n">
-        <v>0.093724</v>
+        <v>0.322049</v>
       </c>
       <c r="H350" s="5" t="n">
-        <v>-0.588165</v>
+        <v>0.087996</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -21716,12 +21782,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>12. Income tax</t>
+          <t>8. Other expenses</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Loss for the year before income tax (recovery) expense</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -21736,10 +21802,10 @@
         </is>
       </c>
       <c r="G351" s="5" t="n">
-        <v>-4.794153</v>
+        <v>0.789471</v>
       </c>
       <c r="H351" s="5" t="n">
-        <v>-2.338294</v>
+        <v>0.656673</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -21765,12 +21831,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Increase in income tax recovery resulting from</t>
+          <t>9. Accounts and other receivables</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Income tax (recovery) expense</t>
+          <t>December 31, 2022 December</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -21785,10 +21851,10 @@
         </is>
       </c>
       <c r="G352" s="5" t="n">
-        <v>0.093724</v>
+        <v>0.002021</v>
       </c>
       <c r="H352" s="5" t="n">
-        <v>-0.588165</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -21814,12 +21880,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>9. Accounts and other receivables</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Losses carried forward</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -21834,10 +21900,10 @@
         </is>
       </c>
       <c r="G353" s="5" t="n">
-        <v>2.094611</v>
+        <v>0.289062</v>
       </c>
       <c r="H353" s="5" t="n">
-        <v>4.733573</v>
+        <v>0.261657</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -21863,12 +21929,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>9. Accounts and other receivables</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Provision for expected credit losses</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -21883,10 +21949,10 @@
         </is>
       </c>
       <c r="G354" s="5" t="n">
-        <v>0.807597</v>
+        <v>-0.1194</v>
       </c>
       <c r="H354" s="5" t="n">
-        <v>0.672524</v>
+        <v>-0.083325</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -21912,12 +21978,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>9. Accounts and other receivables</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
+          <t>Accounts and other receivables</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -21931,13 +21997,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G355" s="5" t="n">
+        <v>0.169662</v>
       </c>
       <c r="H355" s="5" t="n">
-        <v>0.673571</v>
+        <v>0.178332</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -21963,15 +22027,19 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>12. Income tax</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Financing costs</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>Current income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -21983,12 +22051,10 @@
         </is>
       </c>
       <c r="G356" s="5" t="n">
-        <v>1.222982</v>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.133746</v>
+      </c>
+      <c r="H356" s="5" t="n">
+        <v>-0.057031</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -22014,15 +22080,19 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>12. Income tax</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -22033,13 +22103,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G357" s="5" t="n">
+        <v>-0.040022</v>
       </c>
       <c r="H357" s="5" t="n">
-        <v>0.053383</v>
+        <v>-0.531134</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -22065,15 +22133,19 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
+          <t>12. Income tax</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Total unrecognized temporary deductible differences</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -22085,10 +22157,10 @@
         </is>
       </c>
       <c r="G358" s="5" t="n">
-        <v>4.12519</v>
+        <v>0.093724</v>
       </c>
       <c r="H358" s="5" t="n">
-        <v>6.133051</v>
+        <v>-0.588165</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -22114,15 +22186,19 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>12. Income tax</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Contingent consideration payable</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
+          <t>Loss for the year before income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -22134,12 +22210,10 @@
         </is>
       </c>
       <c r="G359" s="5" t="n">
-        <v>0.226448</v>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.794153</v>
+      </c>
+      <c r="H359" s="5" t="n">
+        <v>-2.338294</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
@@ -22165,15 +22239,19 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>following</t>
+          <t>Increase in income tax recovery resulting from</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Income tax credits</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Income tax (recovery) expense</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -22185,12 +22263,10 @@
         </is>
       </c>
       <c r="G360" s="5" t="n">
-        <v>-0.071767</v>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.093724</v>
+      </c>
+      <c r="H360" s="5" t="n">
+        <v>-0.588165</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
@@ -22216,12 +22292,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>of PersistIQ.</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>up to an aggregate of 2,590,389 common shares, representing 5% of the issued and outstanding shares of the Company as at June 3, 2021, for a one-year period from June 11, 2021 to June</t>
+          <t>Losses carried forward</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -22236,10 +22312,10 @@
         </is>
       </c>
       <c r="G361" s="5" t="n">
-        <v>0.002022</v>
+        <v>2.094611</v>
       </c>
       <c r="H361" s="5" t="n">
-        <v>1e-05</v>
+        <v>4.733573</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
@@ -22265,12 +22341,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>January 19, 2022 200,000 $1.26 4.0 January</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -22285,10 +22361,10 @@
         </is>
       </c>
       <c r="G362" s="5" t="n">
-        <v>0.002032</v>
+        <v>0.807597</v>
       </c>
       <c r="H362" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>0.672524</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
@@ -22314,12 +22390,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>June 14, 2022 12,869 $0.69 4.0 June</t>
+          <t>Property and equipment</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -22333,11 +22409,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G363" s="5" t="n">
-        <v>0.002032</v>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H363" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>0.673571</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -22363,12 +22441,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>September 30, 2022 75,000 $0.70 1.0 September</t>
+          <t>Financing costs</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -22383,10 +22461,12 @@
         </is>
       </c>
       <c r="G364" s="5" t="n">
-        <v>0.002027</v>
-      </c>
-      <c r="H364" s="5" t="n">
-        <v>3e-05</v>
+        <v>1.222982</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -22412,12 +22492,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>November 30, 2022 150,000 $0.80 4.0 November</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -22431,11 +22511,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G365" s="5" t="n">
-        <v>0.002032</v>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H365" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.053383</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -22461,12 +22543,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>Deferred tax assets</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>January 19, 2021 75,000 $2.05 4.0 January</t>
+          <t>Total unrecognized temporary deductible differences</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -22481,10 +22563,10 @@
         </is>
       </c>
       <c r="G366" s="5" t="n">
-        <v>0.002031</v>
+        <v>4.12519</v>
       </c>
       <c r="H366" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>6.133051</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -22510,12 +22592,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>May 3, 2021 190,000 $1.92 4.0 May</t>
+          <t>Contingent consideration payable</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -22530,10 +22612,12 @@
         </is>
       </c>
       <c r="G367" s="5" t="n">
-        <v>0.002031</v>
-      </c>
-      <c r="H367" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.226448</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -22559,12 +22643,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>following</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>June 15, 2021 33,890 $1.52 1.0 June</t>
+          <t>Income tax credits</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -22579,10 +22663,12 @@
         </is>
       </c>
       <c r="G368" s="5" t="n">
-        <v>0.002031</v>
-      </c>
-      <c r="H368" s="5" t="n">
-        <v>1.5e-05</v>
+        <v>-0.071767</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -22608,12 +22694,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>granted                             (in years)</t>
+          <t>of PersistIQ.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>June 15, 2021 235,000 $1.52 4.0 June</t>
+          <t>up to an aggregate of 2,590,389 common shares, representing 5% of the issued and outstanding shares of the Company as at June 3, 2021, for a one-year period from June 11, 2021 to June</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -22628,10 +22714,10 @@
         </is>
       </c>
       <c r="G369" s="5" t="n">
-        <v>0.002031</v>
+        <v>0.002022</v>
       </c>
       <c r="H369" s="5" t="n">
-        <v>1.5e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -22662,7 +22748,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>December 10, 2021 290,000 $1.26 4.0 December</t>
+          <t>January 19, 2022 200,000 $1.26 4.0 January</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -22677,10 +22763,10 @@
         </is>
       </c>
       <c r="G370" s="5" t="n">
-        <v>0.002031</v>
+        <v>0.002032</v>
       </c>
       <c r="H370" s="5" t="n">
-        <v>1e-05</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -22711,7 +22797,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>December 10, 2021 20,000 $1.26 3.0 December</t>
+          <t>June 14, 2022 12,869 $0.69 4.0 June</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -22726,10 +22812,10 @@
         </is>
       </c>
       <c r="G371" s="5" t="n">
-        <v>0.002031</v>
+        <v>0.002032</v>
       </c>
       <c r="H371" s="5" t="n">
-        <v>1e-05</v>
+        <v>1.4e-05</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -22755,12 +22841,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Low         High</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Exercise price</t>
+          <t>September 30, 2022 75,000 $0.70 1.0 September</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -22775,10 +22861,10 @@
         </is>
       </c>
       <c r="G372" s="5" t="n">
-        <v>1.26e-06</v>
+        <v>0.002027</v>
       </c>
       <c r="H372" s="5" t="n">
-        <v>6.9e-07</v>
+        <v>3e-05</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -22804,12 +22890,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Low         High</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Share price</t>
+          <t>November 30, 2022 150,000 $0.80 4.0 November</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -22824,10 +22910,10 @@
         </is>
       </c>
       <c r="G373" s="5" t="n">
-        <v>1.26e-06</v>
+        <v>0.002032</v>
       </c>
       <c r="H373" s="5" t="n">
-        <v>6.9e-07</v>
+        <v>3e-05</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -22853,12 +22939,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Volatility                      63%        67%</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Expected dividend</t>
+          <t>January 19, 2021 75,000 $2.05 4.0 January</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -22873,10 +22959,10 @@
         </is>
       </c>
       <c r="G374" s="5" t="n">
-        <v>0</v>
+        <v>0.002031</v>
       </c>
       <c r="H374" s="5" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -22902,12 +22988,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Volatility                      63%        67%</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Grant date fair value</t>
+          <t>May 3, 2021 190,000 $1.92 4.0 May</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -22922,10 +23008,10 @@
         </is>
       </c>
       <c r="G375" s="5" t="n">
-        <v>7.6e-07</v>
+        <v>0.002031</v>
       </c>
       <c r="H375" s="5" t="n">
-        <v>2.6e-07</v>
+        <v>3e-06</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -22951,12 +23037,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Volatility                      63%        71%</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Expected dividend</t>
+          <t>June 15, 2021 33,890 $1.52 1.0 June</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -22971,10 +23057,10 @@
         </is>
       </c>
       <c r="G376" s="5" t="n">
-        <v>0</v>
+        <v>0.002031</v>
       </c>
       <c r="H376" s="5" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -23000,12 +23086,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Volatility                      63%        71%</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Grant date fair value</t>
+          <t>June 15, 2021 235,000 $1.52 4.0 June</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -23020,10 +23106,10 @@
         </is>
       </c>
       <c r="G377" s="5" t="n">
-        <v>1.26e-06</v>
+        <v>0.002031</v>
       </c>
       <c r="H377" s="5" t="n">
-        <v>5.9e-07</v>
+        <v>1.5e-05</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -23049,12 +23135,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>February 2, 2023 87,587 87,587</t>
+          <t>December 10, 2021 290,000 $1.26 4.0 December</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -23069,10 +23155,10 @@
         </is>
       </c>
       <c r="G378" s="5" t="n">
-        <v>9e-08</v>
+        <v>0.002031</v>
       </c>
       <c r="H378" s="5" t="n">
-        <v>4.699999999999999e-07</v>
+        <v>1e-05</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -23098,12 +23184,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>granted                             (in years)</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>April 1, 2023 64,880 64,880</t>
+          <t>December 10, 2021 20,000 $1.26 3.0 December</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -23118,10 +23204,10 @@
         </is>
       </c>
       <c r="G379" s="5" t="n">
-        <v>2.5e-07</v>
+        <v>0.002031</v>
       </c>
       <c r="H379" s="5" t="n">
-        <v>4.699999999999999e-07</v>
+        <v>1e-05</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -23147,12 +23233,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>Low         High</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>December 1, 2023 17,440 17,440</t>
+          <t>Exercise price</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -23167,10 +23253,10 @@
         </is>
       </c>
       <c r="G380" s="5" t="n">
-        <v>9.200000000000001e-07</v>
+        <v>1.26e-06</v>
       </c>
       <c r="H380" s="5" t="n">
-        <v>5e-08</v>
+        <v>6.9e-07</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -23196,12 +23282,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>Low         High</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>September 30, 2027 75,000 18,750</t>
+          <t>Share price</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -23216,10 +23302,10 @@
         </is>
       </c>
       <c r="G381" s="5" t="n">
-        <v>4.75e-06</v>
+        <v>1.26e-06</v>
       </c>
       <c r="H381" s="5" t="n">
-        <v>7e-07</v>
+        <v>6.9e-07</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -23245,12 +23331,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>Volatility                      63%        67%</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>January 10, 2029 59,504 59,504</t>
+          <t>Expected dividend</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -23265,10 +23351,10 @@
         </is>
       </c>
       <c r="G382" s="5" t="n">
-        <v>6.03e-06</v>
+        <v>0</v>
       </c>
       <c r="H382" s="5" t="n">
-        <v>4.6e-07</v>
+        <v>0</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -23294,12 +23380,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>Volatility                      63%        67%</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>June 15, 2030 51,904 25,952</t>
+          <t>Grant date fair value</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -23314,10 +23400,10 @@
         </is>
       </c>
       <c r="G383" s="5" t="n">
-        <v>7.46e-06</v>
+        <v>7.6e-07</v>
       </c>
       <c r="H383" s="5" t="n">
-        <v>5e-08</v>
+        <v>2.6e-07</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -23343,12 +23429,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>Volatility                      63%        71%</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>June 22, 2030 32,440 16,220</t>
+          <t>Expected dividend</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -23363,10 +23449,10 @@
         </is>
       </c>
       <c r="G384" s="5" t="n">
-        <v>7.48e-06</v>
+        <v>0</v>
       </c>
       <c r="H384" s="5" t="n">
-        <v>4.8e-07</v>
+        <v>0</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
@@ -23392,12 +23478,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>outstanding      exercisable             $   length (years)</t>
+          <t>Volatility                      63%        71%</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>December 29, 2030 2,080,223 1,054,799</t>
+          <t>Grant date fair value</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -23412,10 +23498,10 @@
         </is>
       </c>
       <c r="G385" s="5" t="n">
-        <v>8e-06</v>
+        <v>1.26e-06</v>
       </c>
       <c r="H385" s="5" t="n">
-        <v>2.18e-06</v>
+        <v>5.9e-07</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -23446,7 +23532,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>January 19, 2031 75,000 32,811</t>
+          <t>February 2, 2023 87,587 87,587</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -23461,10 +23547,10 @@
         </is>
       </c>
       <c r="G386" s="5" t="n">
-        <v>8.060000000000001e-06</v>
+        <v>9e-08</v>
       </c>
       <c r="H386" s="5" t="n">
-        <v>2.05e-06</v>
+        <v>4.699999999999999e-07</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -23495,7 +23581,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>May 3, 2031 130,000 48,750</t>
+          <t>April 1, 2023 64,880 64,880</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -23510,10 +23596,10 @@
         </is>
       </c>
       <c r="G387" s="5" t="n">
-        <v>8.34e-06</v>
+        <v>2.5e-07</v>
       </c>
       <c r="H387" s="5" t="n">
-        <v>1.92e-06</v>
+        <v>4.699999999999999e-07</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -23544,7 +23630,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>June 15, 2031 155,000 58,124</t>
+          <t>December 1, 2023 17,440 17,440</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -23559,10 +23645,10 @@
         </is>
       </c>
       <c r="G388" s="5" t="n">
-        <v>8.46e-06</v>
+        <v>9.200000000000001e-07</v>
       </c>
       <c r="H388" s="5" t="n">
-        <v>1.52e-06</v>
+        <v>5e-08</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -23593,7 +23679,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>December 10, 2031 310,000 82,500</t>
+          <t>September 30, 2027 75,000 18,750</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -23608,10 +23694,10 @@
         </is>
       </c>
       <c r="G389" s="5" t="n">
-        <v>8.949999999999999e-06</v>
+        <v>4.75e-06</v>
       </c>
       <c r="H389" s="5" t="n">
-        <v>1.26e-06</v>
+        <v>7e-07</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -23642,7 +23728,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>January 19, 2032 200,000 -</t>
+          <t>January 10, 2029 59,504 59,504</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -23657,10 +23743,10 @@
         </is>
       </c>
       <c r="G390" s="5" t="n">
-        <v>9.06e-06</v>
+        <v>6.03e-06</v>
       </c>
       <c r="H390" s="5" t="n">
-        <v>1.26e-06</v>
+        <v>4.6e-07</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -23691,7 +23777,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>June 14, 2032 12,869 -</t>
+          <t>June 15, 2030 51,904 25,952</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -23706,10 +23792,10 @@
         </is>
       </c>
       <c r="G391" s="5" t="n">
-        <v>9.460000000000001e-06</v>
+        <v>7.46e-06</v>
       </c>
       <c r="H391" s="5" t="n">
-        <v>6.9e-07</v>
+        <v>5e-08</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -23740,7 +23826,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>November 30, 2032 150,000 -</t>
+          <t>June 22, 2030 32,440 16,220</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -23755,10 +23841,10 @@
         </is>
       </c>
       <c r="G392" s="5" t="n">
-        <v>9.92e-06</v>
+        <v>7.48e-06</v>
       </c>
       <c r="H392" s="5" t="n">
-        <v>8.000000000000001e-07</v>
+        <v>4.8e-07</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -23784,12 +23870,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>h) Restricted Share Units (“RSUs”)</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>The changes in RSUs during the year ended December 31, 2022 and the year ended December</t>
+          <t>December 29, 2030 2,080,223 1,054,799</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -23804,10 +23890,10 @@
         </is>
       </c>
       <c r="G393" s="5" t="n">
-        <v>0.002021</v>
+        <v>8e-06</v>
       </c>
       <c r="H393" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>2.18e-06</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -23833,12 +23919,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>were as follows</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>December 31, 2022 December</t>
+          <t>January 19, 2031 75,000 32,811</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -23853,10 +23939,10 @@
         </is>
       </c>
       <c r="G394" s="5" t="n">
-        <v>0.002021</v>
+        <v>8.060000000000001e-06</v>
       </c>
       <c r="H394" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>2.05e-06</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -23882,12 +23968,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Number of RSUs   Number of RSUs</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Balance outstanding, beginning of year</t>
+          <t>May 3, 2031 130,000 48,750</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -23901,15 +23987,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G395" s="5" t="n">
+        <v>8.34e-06</v>
+      </c>
+      <c r="H395" s="5" t="n">
+        <v>1.92e-06</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -23935,12 +24017,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Number of RSUs   Number of RSUs</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Units granted</t>
+          <t>June 15, 2031 155,000 58,124</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -23954,13 +24036,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G396" s="5" t="n">
+        <v>8.46e-06</v>
       </c>
       <c r="H396" s="5" t="n">
-        <v>0.505</v>
+        <v>1.52e-06</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -23986,12 +24066,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Number of RSUs   Number of RSUs</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Units forfeited</t>
+          <t>December 10, 2031 310,000 82,500</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -24005,15 +24085,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G397" s="5" t="n">
+        <v>8.949999999999999e-06</v>
+      </c>
+      <c r="H397" s="5" t="n">
+        <v>1.26e-06</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -24039,12 +24115,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Number of RSUs   Number of RSUs</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Units vested</t>
+          <t>January 19, 2032 200,000 -</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -24058,15 +24134,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G398" s="5" t="n">
+        <v>9.06e-06</v>
+      </c>
+      <c r="H398" s="5" t="n">
+        <v>1.26e-06</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -24092,12 +24164,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Number of RSUs   Number of RSUs</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Balance outstanding, end of year</t>
+          <t>June 14, 2032 12,869 -</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -24111,13 +24183,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G399" s="5" t="n">
+        <v>9.460000000000001e-06</v>
       </c>
       <c r="H399" s="5" t="n">
-        <v>0.505</v>
+        <v>6.9e-07</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -24143,12 +24213,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>i)  Performance Share Units (“PSUs”)</t>
+          <t>outstanding      exercisable             $   length (years)</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>The changes in PSUs during the year ended December 31, 2022 and the year ended December</t>
+          <t>November 30, 2032 150,000 -</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -24163,10 +24233,10 @@
         </is>
       </c>
       <c r="G400" s="5" t="n">
-        <v>0.002021</v>
+        <v>9.92e-06</v>
       </c>
       <c r="H400" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>8.000000000000001e-07</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -24192,12 +24262,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Number of PSUs   Number of PSUs</t>
+          <t>h) Restricted Share Units (“RSUs”)</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Balance outstanding, beginning of year</t>
+          <t>The changes in RSUs during the year ended December 31, 2022 and the year ended December</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -24211,15 +24281,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G401" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="H401" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -24245,12 +24311,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Number of PSUs   Number of PSUs</t>
+          <t>were as follows</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Units granted</t>
+          <t>December 31, 2022 December</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -24264,13 +24330,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G402" s="5" t="n">
+        <v>0.002021</v>
       </c>
       <c r="H402" s="5" t="n">
-        <v>1.15</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -24296,12 +24360,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Number of PSUs   Number of PSUs</t>
+          <t>Number of RSUs   Number of RSUs</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Units forfeited</t>
+          <t>Balance outstanding, beginning of year</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -24349,12 +24413,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Number of PSUs   Number of PSUs</t>
+          <t>Number of RSUs   Number of RSUs</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Units vested</t>
+          <t>Units granted</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -24373,10 +24437,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H404" s="5" t="n">
+        <v>0.505</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -24402,12 +24464,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Number of PSUs   Number of PSUs</t>
+          <t>Number of RSUs   Number of RSUs</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Balance outstanding, end of year</t>
+          <t>Units forfeited</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -24426,8 +24488,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H405" s="5" t="n">
-        <v>1.15</v>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -24453,12 +24517,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Key management compensation</t>
+          <t>Number of RSUs   Number of RSUs</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>December 31, 2022 December</t>
+          <t>Units vested</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -24472,11 +24536,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G406" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="H406" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -24502,12 +24570,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Key management compensation</t>
+          <t>Number of RSUs   Number of RSUs</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Salaries, wages, and benefits</t>
+          <t>Balance outstanding, end of year</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -24521,11 +24589,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G407" s="5" t="n">
-        <v>0.642274</v>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H407" s="5" t="n">
-        <v>0.73545</v>
+        <v>0.505</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -24551,12 +24621,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Key management compensation</t>
+          <t>i)  Performance Share Units (“PSUs”)</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Subcontractor and director fees</t>
+          <t>The changes in PSUs during the year ended December 31, 2022 and the year ended December</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -24571,10 +24641,10 @@
         </is>
       </c>
       <c r="G408" s="5" t="n">
-        <v>0.214622</v>
+        <v>0.002021</v>
       </c>
       <c r="H408" s="5" t="n">
-        <v>0.240043</v>
+        <v>3.1e-05</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -24600,12 +24670,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Key management compensation</t>
+          <t>Number of PSUs   Number of PSUs</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Balance outstanding, beginning of year</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -24619,11 +24689,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G409" s="5" t="n">
-        <v>1.649902</v>
-      </c>
-      <c r="H409" s="5" t="n">
-        <v>0.712415</v>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -24649,12 +24723,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Key management compensation</t>
+          <t>Number of PSUs   Number of PSUs</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Units granted</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -24668,11 +24742,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G410" s="5" t="n">
-        <v>2.506798</v>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H410" s="5" t="n">
-        <v>1.687908</v>
+        <v>1.15</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -24696,18 +24772,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Number of PSUs   Number of PSUs</t>
+        </is>
+      </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>For the year ended December 31, 2019 and period from the date of incorporation (June</t>
+          <t>Units forfeited</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
-      <c r="E411" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F411" s="5" t="n">
-        <v>2e-05</v>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -24741,18 +24825,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Number of PSUs   Number of PSUs</t>
+        </is>
+      </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>to December</t>
+          <t>Units vested</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
-      <c r="E412" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F412" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -24788,34 +24880,32 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Number of PSUs   Number of PSUs</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E413" s="5" t="n">
-        <v>0.08709600000000001</v>
-      </c>
-      <c r="F413" s="5" t="n">
-        <v>0.04553</v>
+          <t>Balance outstanding, end of year</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H413" s="5" t="n">
+        <v>1.15</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -24841,12 +24931,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Key management compensation</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>December 31, 2022 December</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -24855,18 +24945,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F414" s="5" t="n">
-        <v>0.070713</v>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G414" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -24892,36 +24980,30 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Key management compensation</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Salaries, wages, and benefits</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F415" s="5" t="n">
-        <v>0.018209</v>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G415" s="5" t="n">
+        <v>0.642274</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>0.73545</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -24947,30 +25029,34 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Key management compensation</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Bank fees</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
-      <c r="E416" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="F416" s="5" t="n">
-        <v>3.5e-05</v>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Subcontractor and director fees</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G416" s="5" t="n">
+        <v>0.214622</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>0.240043</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -24996,34 +25082,30 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Key management compensation</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E417" s="5" t="n">
-        <v>0.087107</v>
-      </c>
-      <c r="F417" s="5" t="n">
-        <v>0.134487</v>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G417" s="5" t="n">
+        <v>1.649902</v>
+      </c>
+      <c r="H417" s="5" t="n">
+        <v>0.712415</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -25049,34 +25131,30 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Key management compensation</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E418" s="5" t="n">
-        <v>-0.087107</v>
-      </c>
-      <c r="F418" s="5" t="n">
-        <v>-0.134487</v>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G418" s="5" t="n">
+        <v>2.506798</v>
+      </c>
+      <c r="H418" s="5" t="n">
+        <v>1.687908</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -25100,24 +25178,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>General and administrative expenses</t>
-        </is>
-      </c>
+      <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share $</t>
+          <t>For the year ended December 31, 2019 and period from the date of incorporation (June</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E419" s="5" t="n">
+        <v>0.002018</v>
       </c>
       <c r="F419" s="5" t="n">
-        <v>-2e-08</v>
+        <v>2e-05</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -25151,50 +25223,786 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>to December</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F420" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="n">
+        <v>0.08709600000000001</v>
+      </c>
+      <c r="F421" s="5" t="n">
+        <v>0.04553</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F422" s="5" t="n">
+        <v>0.070713</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F423" s="5" t="n">
+        <v>0.018209</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Bank fees</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="F424" s="5" t="n">
+        <v>3.5e-05</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E425" s="5" t="n">
+        <v>0.087107</v>
+      </c>
+      <c r="F425" s="5" t="n">
+        <v>0.134487</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E426" s="5" t="n">
+        <v>-0.087107</v>
+      </c>
+      <c r="F426" s="5" t="n">
+        <v>-0.134487</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Basic and diluted net loss per share $</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F427" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
         <is>
           <t>Basic and diluted weighted average</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
+      <c r="C428" t="inlineStr">
         <is>
           <t>Basic and diluted weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
+      <c r="D428" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F420" s="5" t="n">
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F428" s="5" t="n">
         <v>5.496264</v>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K420" t="inlineStr">
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E429" s="5" t="n">
+        <v>0.08709500000000001</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Bank fees</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E431" s="5" t="n">
+        <v>0.087107</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E432" s="5" t="n">
+        <v>-0.087107</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Basic and diluted net loss and comprehensive loss per share $</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Basic and diluted weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
         <is>
           <t>-</t>
         </is>
